--- a/data/processed/positivacao/2024-12_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2024-12_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -26635,7 +26635,7 @@
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B1012" t="inlineStr"/>
@@ -37675,7 +37675,7 @@
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1437" t="inlineStr"/>
@@ -66047,7 +66047,7 @@
     <row r="2529">
       <c r="A2529" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2529" t="inlineStr"/>
@@ -67640,12 +67640,12 @@
       <c r="A2591" t="inlineStr"/>
       <c r="B2591" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 6 cliente(s), não positivou 88 cliente(s) - Total vendido: R$ 5.046,71
+          <t>Vendedor 1 - VENDEDOR 01: positivou 6 cliente(s), não positivou 88 cliente(s) - Total vendido: R$ 5.046,71
 Vendedor 18 - LOJA: positivou 235 cliente(s), não positivou 673 cliente(s) - Total vendido: R$ 89.059,15
-Vendedor 3 - FERNANDA: positivou 114 cliente(s), não positivou 310 cliente(s) - Total vendido: R$ 181.296,64
-Vendedor 4 - DANIELA: positivou 125 cliente(s), não positivou 523 cliente(s) - Total vendido: R$ 73.088,31
+Vendedor 3 - VENDEDOR 03: positivou 114 cliente(s), não positivou 310 cliente(s) - Total vendido: R$ 181.296,64
+Vendedor 4 - VENDEDOR 04: positivou 125 cliente(s), não positivou 523 cliente(s) - Total vendido: R$ 73.088,31
 Vendedor 5 - SITE: positivou 3 cliente(s), não positivou 439 cliente(s) - Total vendido: R$ 2.282,89
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 60 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 60 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2591" t="inlineStr"/>
